--- a/Jogoo School Students Performance (Autosaved).xlsx
+++ b/Jogoo School Students Performance (Autosaved).xlsx
@@ -13,14 +13,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet 2" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.0" hidden="1">Sheet1!$C$57:$M$57</definedName>
     <definedName name="_xlchart.1" hidden="1">Sheet1!$C$57:$M$57</definedName>
     <definedName name="_xlchart.2" hidden="1">Sheet1!$C$57:$M$57</definedName>
-    <definedName name="_xlchart.3" hidden="1">Sheet1!$C$57:$M$57</definedName>
     <definedName name="_xlcn.WorksheetConnection_JogooSchoolStudentsPerformance.xlsxTable11" hidden="1">Table1[]</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
